--- a/Docs/Opentrons Program Templates.xlsx
+++ b/Docs/Opentrons Program Templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/dennis_ad_unc_edu/Documents/Projects/Programs/Opentrons_Programs/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{D985E8EB-94F2-4441-A4EC-A5C038F7B2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02BBD2DE-30AF-4362-9798-8C5BC16CC580}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{D985E8EB-94F2-4441-A4EC-A5C038F7B2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC444F14-1D70-5EF9-A0A9-12C597F71E0F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1058,6 +1058,12 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1066,9 +1072,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -1083,9 +1086,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2088,7 +2088,7 @@
       <c r="A24" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="82">
+      <c r="B24" s="73">
         <v>1</v>
       </c>
     </row>
@@ -3378,24 +3378,24 @@
       <c r="B1" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -3418,123 +3418,123 @@
       <c r="A6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="76"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="76"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="76"/>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
     </row>
     <row r="18" spans="1:6" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
@@ -3598,12 +3598,12 @@
       <c r="B27" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="76" t="s">
+      <c r="C27" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
@@ -3612,10 +3612,10 @@
       <c r="B28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
@@ -4907,6 +4907,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="C27:F28"/>
@@ -4916,12 +4922,6 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:B3 B21:B22 B27:B29 B40:B43">
     <cfRule type="containsBlanks" dxfId="16" priority="8">
@@ -4995,24 +4995,24 @@
       <c r="B1" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -5036,12 +5036,12 @@
       <c r="A6" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
     </row>
@@ -5049,110 +5049,110 @@
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
       <c r="F7" s="56"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
       <c r="F8" s="56"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
       <c r="F9" s="56"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="76"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
       <c r="F10" s="56"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
       <c r="F11" s="56"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="76"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
       <c r="F12" s="56"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
       <c r="F13" s="56"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
       <c r="F14" s="56"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
       <c r="F15" s="56"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="76"/>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
       <c r="F16" s="56"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
       <c r="F17" s="56"/>
     </row>
     <row r="18" spans="1:7" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
@@ -5220,12 +5220,12 @@
       <c r="B27" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="76" t="s">
+      <c r="C27" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
@@ -5234,10 +5234,10 @@
       <c r="B28" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
@@ -8707,6 +8707,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="C27:F28"/>
     <mergeCell ref="B15:E15"/>
@@ -8717,11 +8722,6 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B14:E14"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B2:B3 B27:B28 B40:B42 B58:B61">
@@ -8849,135 +8849,135 @@
       <c r="A6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="76"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="76"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="76"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="76"/>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="76"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
     </row>
     <row r="18" spans="1:7" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
@@ -9047,12 +9047,12 @@
       <c r="B27" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="76" t="s">
+      <c r="C27" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
@@ -9061,10 +9061,10 @@
       <c r="B28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
@@ -9152,11 +9152,11 @@
       <c r="D37" s="2"/>
     </row>
     <row r="38" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="80" t="s">
+      <c r="A38" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="80"/>
-      <c r="C38" s="80"/>
+      <c r="B38" s="81"/>
+      <c r="C38" s="81"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -9219,7 +9219,7 @@
       <c r="B46" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="77" t="s">
+      <c r="C46" s="78" t="s">
         <v>157</v>
       </c>
       <c r="D46" s="37"/>
@@ -9231,7 +9231,7 @@
       <c r="B47" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="78"/>
+      <c r="C47" s="79"/>
       <c r="D47" s="37"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -9241,7 +9241,7 @@
       <c r="B48" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="78"/>
+      <c r="C48" s="79"/>
       <c r="D48" s="37"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -9251,7 +9251,7 @@
       <c r="B49" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="78"/>
+      <c r="C49" s="79"/>
       <c r="D49" s="37"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -9261,7 +9261,7 @@
       <c r="B50" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="78"/>
+      <c r="C50" s="79"/>
       <c r="D50" s="37"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -9271,7 +9271,7 @@
       <c r="B51" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="78"/>
+      <c r="C51" s="79"/>
       <c r="D51" s="37"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -9281,7 +9281,7 @@
       <c r="B52" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="78"/>
+      <c r="C52" s="79"/>
       <c r="D52" s="37"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -9291,7 +9291,7 @@
       <c r="B53" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="78"/>
+      <c r="C53" s="79"/>
       <c r="D53" s="37"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -9301,7 +9301,7 @@
       <c r="B54" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="78"/>
+      <c r="C54" s="79"/>
       <c r="D54" s="37"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -9311,7 +9311,7 @@
       <c r="B55" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="78"/>
+      <c r="C55" s="79"/>
       <c r="D55" s="37"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -9321,7 +9321,7 @@
       <c r="B56" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C56" s="78"/>
+      <c r="C56" s="79"/>
       <c r="D56" s="37"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -9331,7 +9331,7 @@
       <c r="B57" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C57" s="78"/>
+      <c r="C57" s="79"/>
       <c r="D57" s="37"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -9341,7 +9341,7 @@
       <c r="B58" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C58" s="78"/>
+      <c r="C58" s="79"/>
       <c r="D58" s="37"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -9351,7 +9351,7 @@
       <c r="B59" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C59" s="78"/>
+      <c r="C59" s="79"/>
       <c r="D59" s="37"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -9361,7 +9361,7 @@
       <c r="B60" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C60" s="78"/>
+      <c r="C60" s="79"/>
       <c r="D60" s="37"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -9371,7 +9371,7 @@
       <c r="B61" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C61" s="78"/>
+      <c r="C61" s="79"/>
       <c r="D61" s="37"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -9381,7 +9381,7 @@
       <c r="B62" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C62" s="78"/>
+      <c r="C62" s="79"/>
       <c r="D62" s="37"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -9391,7 +9391,7 @@
       <c r="B63" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C63" s="78"/>
+      <c r="C63" s="79"/>
       <c r="D63" s="37"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -9401,7 +9401,7 @@
       <c r="B64" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="C64" s="78"/>
+      <c r="C64" s="79"/>
       <c r="D64" s="37"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -9411,7 +9411,7 @@
       <c r="B65" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C65" s="78"/>
+      <c r="C65" s="79"/>
       <c r="D65" s="37"/>
     </row>
     <row r="66" spans="1:7" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -9421,7 +9421,7 @@
       <c r="B66" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="C66" s="79"/>
+      <c r="C66" s="80"/>
       <c r="D66" s="38"/>
     </row>
     <row r="67" spans="1:7" s="35" customFormat="1" ht="13" thickTop="1" x14ac:dyDescent="0.25">
@@ -12110,12 +12110,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="18" customFormat="1" ht="20" x14ac:dyDescent="0.4">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
     </row>
     <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
